--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.99955</v>
+        <v>17.09993</v>
       </c>
       <c r="D2" t="n">
-        <v>16.753</v>
+        <v>16.73905</v>
       </c>
       <c r="E2" t="n">
-        <v>16.18706</v>
+        <v>17.04923</v>
       </c>
       <c r="F2" t="n">
-        <v>42.16125</v>
+        <v>42.6984</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05071</v>
+        <v>0.05028</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81757</v>
+        <v>1.81752</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.11042</v>
+        <v>16.89611</v>
       </c>
       <c r="D3" t="n">
-        <v>16.31755</v>
+        <v>16.67962</v>
       </c>
       <c r="E3" t="n">
-        <v>16.69323</v>
+        <v>16.74151</v>
       </c>
       <c r="F3" t="n">
-        <v>42.43081</v>
+        <v>42.52238</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05003</v>
+        <v>0.05057</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80829</v>
+        <v>1.78651</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.73337</v>
+        <v>16.96219</v>
       </c>
       <c r="D4" t="n">
-        <v>16.43071</v>
+        <v>16.65532</v>
       </c>
       <c r="E4" t="n">
-        <v>16.79656</v>
+        <v>16.91775</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82187</v>
+        <v>42.14593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05183</v>
+        <v>0.05097</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82339</v>
+        <v>1.82988</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87867</v>
+        <v>16.54315</v>
       </c>
       <c r="D6" t="n">
-        <v>15.90852</v>
+        <v>16.06487</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38231</v>
+        <v>16.53325</v>
       </c>
       <c r="F6" t="n">
-        <v>21.5351</v>
+        <v>22.13284</v>
       </c>
       <c r="G6" t="n">
-        <v>33.40941</v>
+        <v>34.00404</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.62207</v>
+        <v>16.73574</v>
       </c>
       <c r="D7" t="n">
-        <v>16.16424</v>
+        <v>16.05139</v>
       </c>
       <c r="E7" t="n">
-        <v>16.57266</v>
+        <v>16.26135</v>
       </c>
       <c r="F7" t="n">
-        <v>21.55655</v>
+        <v>22.05794</v>
       </c>
       <c r="G7" t="n">
-        <v>33.57922</v>
+        <v>33.8542</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65435</v>
+        <v>16.71995</v>
       </c>
       <c r="D8" t="n">
-        <v>16.30197</v>
+        <v>15.91636</v>
       </c>
       <c r="E8" t="n">
-        <v>16.11351</v>
+        <v>16.68301</v>
       </c>
       <c r="F8" t="n">
-        <v>21.90499</v>
+        <v>21.5221</v>
       </c>
       <c r="G8" t="n">
-        <v>34.08337</v>
+        <v>33.98976</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61472</v>
+        <v>0.59902</v>
       </c>
       <c r="D10" t="n">
-        <v>1.09943</v>
+        <v>1.11013</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60143</v>
+        <v>0.60339</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1296</v>
+        <v>1.11011</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6141</v>
+        <v>0.59678</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09891</v>
+        <v>1.11137</v>
       </c>
     </row>
   </sheetData>
